--- a/DateBase/orders/Nhat 48_2026-9-9.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-9.xlsx
@@ -518,7 +518,7 @@
     </row>
     <row r="11">
       <c r="C11" t="str">
-        <v>68_粉黛_undefined_Gerbera L._20stems</v>
+        <v>422_粉黛_pink muhly grass_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-9.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-9.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>422_粉黛_pink muhly grass_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0129851010101050</v>
+        <v>0129851010101051</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-9.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-9.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -521,12 +521,179 @@
         <v>422_粉黛_pink muhly grass_undefined_1bunch</v>
       </c>
       <c r="F11" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>550_蕾丝红色_lace flower brown_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>859_喷色小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>653_大丽花 黑_undefined_undefined_5stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>643_巧克力秋英_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>422_粉黛_pink muhly grass_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
         <v>1</v>
+      </c>
+      <c r="C21" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>188_戴安娜_Diana_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>237_酷皮_Kupi_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>616_康乃馨紫精灵_Purple Elves_undefined_20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2</v>
+      </c>
+      <c r="C28" t="str">
+        <v>521_商陆_phytolacca acinosa _undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>433_红豆_Hypericum red_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>433_红豆_Hypericum red_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="C31" t="str" xml:space="preserve">
+        <v xml:space="preserve">542_吊米 红_hanging amaranthus
+red_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +748,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0129851010101051</v>
+        <v>01298510101010510101055551510101061081051015550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-9.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-9.xlsx
@@ -690,6 +690,9 @@
         <v xml:space="preserve">542_吊米 红_hanging amaranthus
 red_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -748,7 +751,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01298510101010510101055551510101061081051015550</v>
+        <v>01298510101010510101055551510101061081051015555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-9.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-9.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -694,9 +694,87 @@
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>18_波浪黄洋桔梗_Wavy Yellow Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="C34" t="str" xml:space="preserve">
+        <v xml:space="preserve">404_小飞燕白色_ delphinium ballkleid
+white_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>771_美洲茶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>615_康乃馨野马_horse_undefined_20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>610_康乃馨黄_yellow_undefined_20stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>609_康乃馨小天使_angle_undefined_20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -751,7 +829,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01298510101010510101055551510101061081051015555</v>
+        <v>012985101010105101010555515101010610810510155551051051055550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-9.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-9.xlsx
@@ -771,6 +771,9 @@
       <c r="C41" t="str">
         <v>609_康乃馨小天使_angle_undefined_20stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -829,7 +832,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>012985101010105101010555515101010610810510155551051051055550</v>
+        <v>012985101010105101010555515101010610810510155551051051055555</v>
       </c>
     </row>
   </sheetData>
